--- a/stories/arbres/TREE-AUT-035.xlsx
+++ b/stories/arbres/TREE-AUT-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lina est avec maman, à l'école. Lina a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina écoute maman. Lina entend les mots : une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-035.xlsx
+++ b/stories/arbres/TREE-AUT-035.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lina est avec maman, à l'école. Lina a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina écoute maman. Lina entend les mots : une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Lina a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Lina rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Lina rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Lina rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Lina a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Lina rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Lina a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Lina rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Lina a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Lina rejoint Léa. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Lina a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Lina rejoint Tom. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Lina a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Lina rejoint Sami. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Lina a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Lina rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Lina a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Lina rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Lina a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Lina rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Lina rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Lina rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-035.xlsx
+++ b/stories/arbres/TREE-AUT-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enchaîner le matin — à l'école</t>
+          <t>Le fil d'argent et le radiateur de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un escargot laisse un fil d'argent sur la vitre de l'école. Nina veut déjà la cour. Papa et maman disent : une étape après l'autre. D'abord le vestiaire, ensuite le jeu.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Lina est avec maman, à l'école. Lina a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina écoute maman. Lina entend les mots : une étape après l'autre.</t>
+          <t>Un fil d'argent traverse la vitre de l'école. Il brille, tout mince, tout lent. Un escargot avance, collé au verre. La vitre est encore un peu grise. Dans la cour, une flaque ronde attend. Elle tient un morceau de ciel. Le préau goutte, tout doux, sur le bois. Les manteaux pendent, lourds, au vestiaire. Un gant rouge a perdu sa paire. Le radiateur fait tic, contre le mur. Il est tiède, tout bas. Papa essuie une botte, sans bruit. Maman ouvre le petit cartable bleu. Tu as vu l'escargot, Nina ? Oui, maman. Il brille. Le radiateur est tiède. Tu le sens ? En ce moment, Nina pose les mains dessus. Ses doigts deviennent un peu roses. Je veux déjà la cour ! D'accord. Une étape après l'autre. D'abord le vestiaire. Ensuite la cour. D'abord le vestiaire. Oui. On fait l'étape dite. Les crochets du vestiaire sont froids. Le gant rouge attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Lina est avec maman, à l'école. Lina a envie de jouer. maman est là, tout près. On va apprendre : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina écoute maman. Lina entend les mots : une étape après l'autre.</t>
+          <t>narrateur|Un fil d'argent traverse la vitre de l'école.
+narrateur|Il brille, tout mince, tout lent.
+narrateur|Un escargot avance, collé au verre.
+narrateur|La vitre est encore un peu grise.
+narrateur|Dans la cour, une flaque ronde attend.
+narrateur|Elle tient un morceau de ciel.
+narrateur|Le préau goutte, tout doux, sur le bois.
+narrateur|Les manteaux pendent, lourds, au vestiaire.
+narrateur|Un gant rouge a perdu sa paire.
+narrateur|Le radiateur fait tic, contre le mur.
+narrateur|Il est tiède, tout bas.
+narrateur|Papa essuie une botte, sans bruit.
+narrateur|Maman ouvre le petit cartable bleu.
+maman|Tu as vu l'escargot, Nina ?
+enfant-f|Oui, maman. Il brille.
+papa|Le radiateur est tiède. Tu le sens ?
+narrateur|En ce moment, Nina pose les mains dessus.
+narrateur|Ses doigts deviennent un peu roses.
+enfant-f|Je veux déjà la cour !
+maman|D'accord. Une étape après l'autre.
+papa|D'abord le vestiaire.
+papa|Ensuite la cour.
+enfant-f|D'abord le vestiaire.
+maman|Oui. On fait l'étape dite.
+narrateur|Les crochets du vestiaire sont froids.
+narrateur|Le gant rouge attend encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1390,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Ils arrivent dans la cour. Nina peut commencer à trois endroits. Le bac à sable, le toboggan, ou les balançoires ? Tu choisis. Ensuite on fait l'étape.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1554,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Ils arrivent dans la cour.
+narrateur|Nina peut commencer à trois endroits.
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|Tu choisis.
+maman|Ensuite on fait l'étape.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Nina s'agenouille près du bac à sable. Le sable est frais, un peu humide. Il coule entre ses doigts. Chh. Une petite pelle jaune attend. D'abord le sable. Ensuite on continue. Une étape après l'autre. Je fais un tas. Nina fait un petit tas rond. Le tas a une ombre, toute courte. Tu as fait l'étape dite. Bravo. On reste près du bac, ensemble. Le sable est doux. Loin, un grelot de vélo sonne une fois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1726,29 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On écoute jusqu'au bout.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina s'agenouille près du bac à sable.
+narrateur|Le sable est frais, un peu humide.
+narrateur|Il coule entre ses doigts.
+narrateur|Chh.
+narrateur|Une petite pelle jaune attend.
+papa|D'abord le sable.
+papa|Ensuite on continue.
+maman|Une étape après l'autre.
+enfant-f|Je fais un tas.
+narrateur|Nina fait un petit tas rond.
+narrateur|Le tas a une ombre, toute courte.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|On reste près du bac, ensemble.
+enfant-f|Le sable est doux.
+narrateur|Loin, un grelot de vélo sonne une fois.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Nina est près du bac à sable. On avance comment ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1929,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Nina est près du bac à sable.
+maman|On avance comment ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. Un grain de sable brille sur son genou. Ensuite, on continue. Oui. On continue, avec nous. C'est plus calme, comme ça. La pelle jaune attend encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2102,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>papa|Oui. Une étape après l'autre.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+narrateur|Un grain de sable brille sur son genou.
+enfant-f|Ensuite, on continue.
+papa|Oui. On continue, avec nous.
+maman|C'est plus calme, comme ça.
+narrateur|La pelle jaune attend encore.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2137,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider, dans la cour. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2301,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider, dans la cour.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2332,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina est encore près du bac à sable. Le ballon rouge attend dans l'herbe courte. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite on joue, tout près. Une étape après l'autre. Nina pose les deux mains dessus. Le ballon fait un petit bruit de peau. Elle le tient contre son manteau. Tu as fait l'étape dite. Bravo. Tu as fini de le tenir ? Oui. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2472,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le ballon rouge attend dans l'herbe courte.
+narrateur|Il est lisse, un peu frais.
+enfant-f|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite on joue, tout près.
+maman|Une étape après l'autre.
+narrateur|Nina pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Elle le tient contre son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de le tenir ?
+enfant-f|Oui.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2519,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2687,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2718,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le ballon rouge vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Un grain de sable colle au ballon, sous le préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,10 +2858,33 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Un grain de sable colle au ballon, sous le préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2794,7 +2909,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le ballon. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3049,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le ballon rouge vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le ballon a une goutte de fontaine dessus. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,10 +3226,33 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le ballon a une goutte de fontaine dessus.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3130,7 +3277,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le ballon. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3417,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3454,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le ballon rouge vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le ballon appuie contre le cartable bleu. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,10 +3594,33 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le ballon appuie contre le cartable bleu.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3466,7 +3645,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le ballon. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3785,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3822,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Nina est encore près du bac à sable. Le seau bleu a une anse qui brille. L'anse est un peu froide. Le seau, maman. D'accord. D'abord l'anse. Ensuite on le pose. Une étape après l'autre. Nina prend l'anse. Ting. Le seau est vide, léger. Elle le pose tout doux, près de ses pieds. Tu as fait l'étape dite. Bravo. Le seau est à sa place ? Oui, papa. Un oiseau crie une fois, tout haut.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3962,29 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le seau bleu a une anse qui brille.
+narrateur|L'anse est un peu froide.
+enfant-f|Le seau, maman.
+maman|D'accord.
+maman|D'abord l'anse.
+maman|Ensuite on le pose.
+papa|Une étape après l'autre.
+narrateur|Nina prend l'anse. Ting.
+narrateur|Le seau est vide, léger.
+narrateur|Elle le pose tout doux, près de ses pieds.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Le seau est à sa place ?
+enfant-f|Oui, papa.
+narrateur|Un oiseau crie une fois, tout haut.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +4009,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3970,7 +4177,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3998,7 +4208,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le seau bleu vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le seau résonne un peu, sous le préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4138,10 +4348,33 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le seau résonne un peu, sous le préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4166,7 +4399,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le seau. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4306,7 +4539,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4334,7 +4576,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le seau bleu vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Une goutte de fontaine tombe dans le seau. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4474,10 +4716,33 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le seau bleu vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Une goutte de fontaine tombe dans le seau.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4502,7 +4767,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le seau. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4642,7 +4907,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4670,7 +4944,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le seau bleu vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le seau se pose à côté du cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4810,10 +5084,33 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le seau se pose à côté du cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4838,7 +5135,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le seau. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4978,7 +5275,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5006,7 +5312,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Nina est encore près du bac à sable. Le doudou beige attend sur le banc du préau. Une oreille est un peu pliée. Le doudou, maman. D'accord. D'abord le prendre. Ensuite le poser près de nous. Une étape après l'autre. Nina prend le doudou. Il sent le lit. Le tissu est doux, un peu chaud. Elle le pose près de maman, tout calme. Tu as fait l'étape dite. Bravo. Il est bien, là ? Oui. Il attend. Le doudou garde l'oreille pliée.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5146,10 +5452,29 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le doudou beige attend sur le banc du préau.
+narrateur|Une oreille est un peu pliée.
+enfant-f|Le doudou, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser près de nous.
+papa|Une étape après l'autre.
+narrateur|Nina prend le doudou. Il sent le lit.
+narrateur|Le tissu est doux, un peu chaud.
+narrateur|Elle le pose près de maman, tout calme.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Il est bien, là ?
+enfant-f|Oui. Il attend.
+narrateur|Le doudou garde l'oreille pliée.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5174,7 +5499,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5342,7 +5667,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5370,7 +5698,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le doudou beige vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le doudou sent le bois sec du préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5510,10 +5838,33 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le doudou sent le bois sec du préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5538,7 +5889,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le doudou. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5678,7 +6029,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5706,7 +6066,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le doudou beige vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le doudou a une goutte sur l'oreille. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5846,10 +6206,33 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le doudou beige vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le doudou a une goutte sur l'oreille.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5874,7 +6257,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le doudou. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6014,7 +6397,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6042,7 +6434,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du bac à sable. Le doudou beige vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le doudou glisse contre le cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6182,10 +6574,33 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du bac à sable.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le doudou glisse contre le cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6210,7 +6625,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le bac à sable. Elle a pris le doudou. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6350,7 +6765,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le bac à sable.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6378,7 +6802,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Nina pose un pied sur la première marche. La marche du toboggan est un peu froide. Le plastique jaune brille, encore mouillé. Une goutte pend sous le rebord. D'abord une marche. Ensuite la suivante. Une étape après l'autre. J'y vais, papa. Nina monte. Une marche. Puis une autre. Ses mains tiennent la rampe lisse. Tu as fait l'étape dite. Bravo. Tu es bien, Nina ? Oui. Je vois la cour. Le ciel dans la flaque est tout petit. Le toboggan sent le plastique tiède.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6518,11 +6942,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On attend son tour.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina pose un pied sur la première marche.
+narrateur|La marche du toboggan est un peu froide.
+narrateur|Le plastique jaune brille, encore mouillé.
+narrateur|Une goutte pend sous le rebord.
+maman|D'abord une marche.
+maman|Ensuite la suivante.
+papa|Une étape après l'autre.
+enfant-f|J'y vais, papa.
+narrateur|Nina monte. Une marche. Puis une autre.
+narrateur|Ses mains tiennent la rampe lisse.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu es bien, Nina ?
+enfant-f|Oui. Je vois la cour.
+narrateur|Le ciel dans la flaque est tout petit.
+narrateur|Le toboggan sent le plastique tiède.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6547,7 +6989,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Nina est près du toboggan. On avance comment ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6703,7 +7145,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Nina est près du toboggan.
+papa|On avance comment ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6731,7 +7174,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. La goutte sous le rebord tombe, plic. Ensuite, on continue. Oui. On continue, avec nous. Une marche, puis l'autre. Le plastique jaune est un peu tiède.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6875,7 +7318,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>maman|Oui. Une étape après l'autre.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+narrateur|La goutte sous le rebord tombe, plic.
+enfant-f|Ensuite, on continue.
+maman|Oui. On continue, avec nous.
+papa|Une marche, puis l'autre.
+narrateur|Le plastique jaune est un peu tiède.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6903,7 +7353,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider, dans la cour. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7067,7 +7517,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider, dans la cour.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7095,7 +7548,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina est encore près du toboggan. Le ballon rouge attend dans l'herbe courte. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite on joue, tout près. Une étape après l'autre. Nina pose les deux mains dessus. Le ballon fait un petit bruit de peau. Elle le tient contre son manteau. Tu as fait l'étape dite. Bravo. Tu as fini de le tenir ? Oui. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7235,10 +7688,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le ballon rouge attend dans l'herbe courte.
+narrateur|Il est lisse, un peu frais.
+enfant-f|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite on joue, tout près.
+maman|Une étape après l'autre.
+narrateur|Nina pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Elle le tient contre son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de le tenir ?
+enfant-f|Oui.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,7 +7735,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7431,7 +7903,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7459,7 +7934,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le ballon rouge vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le ballon roule jusqu'au pilier du préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7599,10 +8074,33 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le ballon roule jusqu'au pilier du préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7627,7 +8125,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le ballon. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7767,7 +8265,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7795,7 +8302,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le ballon rouge vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le ballon tremble un peu, près de l'eau. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7935,10 +8442,33 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le ballon tremble un peu, près de l'eau.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7963,7 +8493,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le ballon. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8103,7 +8633,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8131,7 +8670,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le ballon rouge vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le ballon attend contre le cartable fermé. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8271,10 +8810,33 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le ballon attend contre le cartable fermé.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8299,7 +8861,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le ballon. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8439,7 +9001,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8467,7 +9038,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Nina est encore près du toboggan. Le seau bleu a une anse qui brille. L'anse est un peu froide. Le seau, maman. D'accord. D'abord l'anse. Ensuite on le pose. Une étape après l'autre. Nina prend l'anse. Ting. Le seau est vide, léger. Elle le pose tout doux, près de ses pieds. Tu as fait l'étape dite. Bravo. Le seau est à sa place ? Oui, papa. Un oiseau crie une fois, tout haut.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8607,10 +9178,29 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le seau bleu a une anse qui brille.
+narrateur|L'anse est un peu froide.
+enfant-f|Le seau, maman.
+maman|D'accord.
+maman|D'abord l'anse.
+maman|Ensuite on le pose.
+papa|Une étape après l'autre.
+narrateur|Nina prend l'anse. Ting.
+narrateur|Le seau est vide, léger.
+narrateur|Elle le pose tout doux, près de ses pieds.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Le seau est à sa place ?
+enfant-f|Oui, papa.
+narrateur|Un oiseau crie une fois, tout haut.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8635,7 +9225,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8803,7 +9393,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8831,7 +9424,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le seau bleu vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le seau fait ting, sous le bois du préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8971,10 +9564,33 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le seau fait ting, sous le bois du préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8999,7 +9615,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le seau. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9139,7 +9755,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9167,7 +9792,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le seau bleu vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le seau reçoit une goutte, plic. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9307,10 +9932,33 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le seau bleu vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le seau reçoit une goutte, plic.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9335,7 +9983,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le seau. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9475,7 +10123,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9503,7 +10160,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le seau bleu vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le seau bleu garde le dessin au chaud, à côté. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9643,10 +10300,33 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le seau bleu garde le dessin au chaud, à côté.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9671,7 +10351,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le seau. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9811,7 +10491,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9839,7 +10528,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Nina est encore près du toboggan. Le doudou beige attend sur le banc du préau. Une oreille est un peu pliée. Le doudou, maman. D'accord. D'abord le prendre. Ensuite le poser près de nous. Une étape après l'autre. Nina prend le doudou. Il sent le lit. Le tissu est doux, un peu chaud. Elle le pose près de maman, tout calme. Tu as fait l'étape dite. Bravo. Il est bien, là ? Oui. Il attend. Le doudou garde l'oreille pliée.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9979,10 +10668,29 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le doudou beige attend sur le banc du préau.
+narrateur|Une oreille est un peu pliée.
+enfant-f|Le doudou, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser près de nous.
+papa|Une étape après l'autre.
+narrateur|Nina prend le doudou. Il sent le lit.
+narrateur|Le tissu est doux, un peu chaud.
+narrateur|Elle le pose près de maman, tout calme.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Il est bien, là ?
+enfant-f|Oui. Il attend.
+narrateur|Le doudou garde l'oreille pliée.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10007,7 +10715,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10175,7 +10883,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10203,7 +10914,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le doudou beige vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le doudou s'adosse au pilier, tout calme. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10343,10 +11054,33 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le doudou s'adosse au pilier, tout calme.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10371,7 +11105,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le doudou. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10511,7 +11245,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10539,7 +11282,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le doudou beige vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le doudou écoute la goutte, plic, plic. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10679,10 +11422,33 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le doudou beige vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le doudou écoute la goutte, plic, plic.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10707,7 +11473,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le doudou. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10847,7 +11613,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10875,7 +11650,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près du toboggan. Le doudou beige vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le doudou veille près de la boucle du cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11015,10 +11790,33 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. La lumière est claire. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Nina est encore près du toboggan.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le doudou veille près de la boucle du cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11043,7 +11841,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par le toboggan. Elle a pris le doudou. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11183,7 +11981,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par le toboggan.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11211,7 +12018,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Nina s'approche des balançoires. Les chaînes font un petit cling. Le siège en bois est encore frais. Une ombre d'oiseau passe dessus. D'abord s'asseoir. Ensuite on se balance, tout doux. Une étape après l'autre. Je m'assois. Nina s'assoit. Les chaînes sont froides. Elle pose les deux mains dessus. Tu as fait l'étape dite. Bravo. On reste près de toi. Ça bouge un peu. Le gant rouge pend encore au vestiaire. La cour sent l'herbe mouillée.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11351,11 +12158,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : une étape après l'autre. Voici le geste : faire l'étape dite. On montre du doigt, sans courir.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina s'approche des balançoires.
+narrateur|Les chaînes font un petit cling.
+narrateur|Le siège en bois est encore frais.
+narrateur|Une ombre d'oiseau passe dessus.
+papa|D'abord s'asseoir.
+papa|Ensuite on se balance, tout doux.
+maman|Une étape après l'autre.
+enfant-f|Je m'assois.
+narrateur|Nina s'assoit. Les chaînes sont froides.
+narrateur|Elle pose les deux mains dessus.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|On reste près de toi.
+enfant-f|Ça bouge un peu.
+narrateur|Le gant rouge pend encore au vestiaire.
+narrateur|La cour sent l'herbe mouillée.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11380,7 +12205,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Enchaîner le matin.</t>
+          <t>Nina est près des balançoires. On avance comment ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11536,7 +12361,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Enchaîner le matin.</t>
+          <t>narrateur|Nina est près des balançoires.
+maman|On avance comment ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11564,7 +12390,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>Oui. Une étape après l'autre. Tu as fait l'étape dite. Bravo. Les chaînes se taisent un moment. Ensuite, on continue. Oui. On continue, avec nous. On reste ensemble, tout près. Le siège en bois redevient calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11708,7 +12534,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : faire l'étape dite. Lina respire. Lina retient : une étape après l'autre. On continue, avec maman.</t>
+          <t>papa|Oui. Une étape après l'autre.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+narrateur|Les chaînes se taisent un moment.
+enfant-f|Ensuite, on continue.
+papa|Oui. On continue, avec nous.
+maman|On reste ensemble, tout près.
+narrateur|Le siège en bois redevient calme.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11736,7 +12569,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Un objet peut aider, dans la cour. Le ballon, le seau, ou le doudou ? On prend un objet. Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11900,7 +12733,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Un objet peut aider, dans la cour.
+papa|Le ballon, le seau, ou le doudou ?
+maman|On prend un objet.
+maman|Puis l'étape suivante.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11928,7 +12764,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina est encore près des balançoires. Le ballon rouge attend dans l'herbe courte. Il est lisse, un peu frais. Le ballon, papa. D'accord. D'abord le tenir. Ensuite on joue, tout près. Une étape après l'autre. Nina pose les deux mains dessus. Le ballon fait un petit bruit de peau. Elle le tient contre son manteau. Tu as fait l'étape dite. Bravo. Tu as fini de le tenir ? Oui. Le ballon reste à sa place, près de maman.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12068,10 +12904,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On rit un peu. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le ballon rouge attend dans l'herbe courte.
+narrateur|Il est lisse, un peu frais.
+enfant-f|Le ballon, papa.
+papa|D'accord.
+papa|D'abord le tenir.
+papa|Ensuite on joue, tout près.
+maman|Une étape après l'autre.
+narrateur|Nina pose les deux mains dessus.
+narrateur|Le ballon fait un petit bruit de peau.
+narrateur|Elle le tient contre son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tu as fini de le tenir ?
+enfant-f|Oui.
+narrateur|Le ballon reste à sa place, près de maman.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12096,7 +12951,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +13119,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12292,7 +13150,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le ballon rouge vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le ballon se cale entre deux piliers. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12432,10 +13290,33 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le ballon se cale entre deux piliers.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12460,7 +13341,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le ballon. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12600,7 +13481,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12628,7 +13518,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le ballon rouge vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Les chaînes se taisent près de la fontaine. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12768,10 +13658,33 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Les chaînes se taisent près de la fontaine.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12796,7 +13709,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le ballon. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12936,7 +13849,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12964,7 +13886,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le ballon rouge vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le ballon rouge garde le cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13104,10 +14026,33 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le ballon rouge vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le ballon rouge garde le cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13132,7 +14077,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le ballon. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13272,7 +14217,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le ballon.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13300,7 +14254,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Nina est encore près des balançoires. Le seau bleu a une anse qui brille. L'anse est un peu froide. Le seau, maman. D'accord. D'abord l'anse. Ensuite on le pose. Une étape après l'autre. Nina prend l'anse. Ting. Le seau est vide, léger. Elle le pose tout doux, près de ses pieds. Tu as fait l'étape dite. Bravo. Le seau est à sa place ? Oui, papa. Un oiseau crie une fois, tout haut.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13440,10 +14394,29 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tait une seconde. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le seau bleu a une anse qui brille.
+narrateur|L'anse est un peu froide.
+enfant-f|Le seau, maman.
+maman|D'accord.
+maman|D'abord l'anse.
+maman|Ensuite on le pose.
+papa|Une étape après l'autre.
+narrateur|Nina prend l'anse. Ting.
+narrateur|Le seau est vide, léger.
+narrateur|Elle le pose tout doux, près de ses pieds.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Le seau est à sa place ?
+enfant-f|Oui, papa.
+narrateur|Un oiseau crie une fois, tout haut.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13468,7 +14441,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13636,7 +14609,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13664,7 +14640,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le seau bleu vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le seau pose son anse sur le banc du préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13804,10 +14780,33 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le seau pose son anse sur le banc du préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13832,7 +14831,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le seau. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13972,7 +14971,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14000,7 +15008,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le seau bleu vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. L'eau de la fontaine chante dans le seau. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14140,10 +15148,33 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le seau bleu vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|L'eau de la fontaine chante dans le seau.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14168,7 +15199,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le seau. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14308,7 +15339,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14336,7 +15376,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le seau bleu vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le seau bleu s'assoit près du cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14476,10 +15516,33 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. La lumière est claire. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le seau bleu vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le seau bleu s'assoit près du cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14504,7 +15567,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le seau. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14644,7 +15707,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le seau.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14672,7 +15744,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
+          <t>Nina est encore près des balançoires. Le doudou beige attend sur le banc du préau. Une oreille est un peu pliée. Le doudou, maman. D'accord. D'abord le prendre. Ensuite le poser près de nous. Une étape après l'autre. Nina prend le doudou. Il sent le lit. Le tissu est doux, un peu chaud. Elle le pose près de maman, tout calme. Tu as fait l'étape dite. Bravo. Il est bien, là ? Oui. Il attend. Le doudou garde l'oreille pliée.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14812,10 +15884,29 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : faire l'étape dite. Lina répète tout bas : une étape après l'autre. On se tient la main. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le doudou beige attend sur le banc du préau.
+narrateur|Une oreille est un peu pliée.
+enfant-f|Le doudou, maman.
+maman|D'accord.
+maman|D'abord le prendre.
+maman|Ensuite le poser près de nous.
+papa|Une étape après l'autre.
+narrateur|Nina prend le doudou. Il sent le lit.
+narrateur|Le tissu est doux, un peu chaud.
+narrateur|Elle le pose près de maman, tout calme.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Il est bien, là ?
+enfant-f|Oui. Il attend.
+narrateur|Le doudou garde l'oreille pliée.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14840,7 +15931,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le matin peut encore avancer, à l'école. Le préau, la fontaine, ou le cartable ? On fait l'étape. Une après l'autre.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15008,7 +16099,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le matin peut encore avancer, à l'école.
+papa|Le préau, la fontaine, ou le cartable ?
+maman|On fait l'étape.
+maman|Une après l'autre.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15036,7 +16130,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le doudou beige vient avec elle. Le préau a des piliers en bois clair. Le sol dessous est sec, enfin. Le doudou a une place au sec, sous le préau. D'abord sous le préau. Ensuite on s'assoit. Une étape après l'autre. J'y vais. Nina marche jusqu'au pilier. Ses bottes font toc toc, plus sourd. Elle s'assoit. Le bois est lisse. Tu as fait l'étape dite. Bravo. Tu as faim, un peu ? Oui. Un petit bout. Maman sort un morceau de pomme. La pomme est froide, un peu sucrée. Merci, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15176,10 +16270,33 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Tom. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le préau a des piliers en bois clair.
+narrateur|Le sol dessous est sec, enfin.
+narrateur|Le doudou a une place au sec, sous le préau.
+papa|D'abord sous le préau.
+papa|Ensuite on s'assoit.
+maman|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina marche jusqu'au pilier.
+narrateur|Ses bottes font toc toc, plus sourd.
+narrateur|Elle s'assoit. Le bois est lisse.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu as faim, un peu ?
+enfant-f|Oui. Un petit bout.
+narrateur|Maman sort un morceau de pomme.
+narrateur|La pomme est froide, un peu sucrée.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15204,7 +16321,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le doudou. Elle a fait l'étape du préau. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le préau sent encore le bois mouillé. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15344,7 +16461,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du préau.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le préau sent encore le bois mouillé.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15372,7 +16498,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le doudou beige vient avec elle. La fontaine de la cour est en pierre grise. Une goutte pend, puis tombe. Plic. Le doudou se cache un peu de la goutte. D'abord les mains. Ensuite l'eau, tout doux. Une étape après l'autre. J'y vais. Nina va jusqu'à la pierre. L'eau est froide sur ses doigts. Elle essuie ses mains sur son manteau. Tu as fait l'étape dite. Bravo. Tes mains sont propres ? Oui, maman. Elles sont froides. Papa tend un coin de mouchoir. Le mouchoir sent le savon. Merci, Nina. Tu as fait du bon travail. Une autre goutte tombe, toute seule.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15512,10 +16638,33 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Léa. La lumière est claire. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le doudou beige vient avec elle.
+narrateur|La fontaine de la cour est en pierre grise.
+narrateur|Une goutte pend, puis tombe. Plic.
+narrateur|Le doudou se cache un peu de la goutte.
+maman|D'abord les mains.
+maman|Ensuite l'eau, tout doux.
+papa|Une étape après l'autre.
+enfant-f|J'y vais.
+narrateur|Nina va jusqu'à la pierre.
+narrateur|L'eau est froide sur ses doigts.
+narrateur|Elle essuie ses mains sur son manteau.
+papa|Tu as fait l'étape dite.
+papa|Bravo.
+maman|Tes mains sont propres ?
+enfant-f|Oui, maman. Elles sont froides.
+narrateur|Papa tend un coin de mouchoir.
+narrateur|Le mouchoir sent le savon.
+maman|Merci, Nina. Tu as fait du bon travail.
+narrateur|Une autre goutte tombe, toute seule.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15540,7 +16689,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le doudou. Elle a fait l'étape de la fontaine. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Une goutte tombe encore, toute seule. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15680,7 +16829,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape de la fontaine.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Une goutte tombe encore, toute seule.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15708,7 +16866,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
+          <t>Nina est encore près des balançoires. Le doudou beige vient avec elle. Le cartable bleu attend près du vestiaire. La boucle est un peu froide. Le doudou reste dehors, tout près du cartable. D'abord ouvrir. Ensuite on range le dessin. Une étape après l'autre. J'ouvre. Nina ouvre la boucle. Clic. Un dessin à la craie est plié dedans. Elle le pousse tout doux, au fond. Tu as fait l'étape dite. Bravo. Tu refermes ? Oui. Clic. Le cartable est fermé, un peu lourd. Le gant rouge a retrouvé sa paire. Merci, Nina. Tu as fait du bon travail. Le vestiaire sent la laine mouillée.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15848,10 +17006,33 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint Sami. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Enchaîner le matin. Voici le geste : faire l'étape dite. Lina a entendu : une étape après l'autre. Lina dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Nina est encore près des balançoires.
+narrateur|Le doudou beige vient avec elle.
+narrateur|Le cartable bleu attend près du vestiaire.
+narrateur|La boucle est un peu froide.
+narrateur|Le doudou reste dehors, tout près du cartable.
+papa|D'abord ouvrir.
+papa|Ensuite on range le dessin.
+maman|Une étape après l'autre.
+enfant-f|J'ouvre.
+narrateur|Nina ouvre la boucle. Clic.
+narrateur|Un dessin à la craie est plié dedans.
+narrateur|Elle le pousse tout doux, au fond.
+maman|Tu as fait l'étape dite.
+maman|Bravo.
+papa|Tu refermes ?
+enfant-f|Oui. Clic.
+narrateur|Le cartable est fermé, un peu lourd.
+narrateur|Le gant rouge a retrouvé sa paire.
+papa|Merci, Nina. Tu as fait du bon travail.
+narrateur|Le vestiaire sent la laine mouillée.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15876,7 +17057,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina est passée par les balançoires. Elle a pris le doudou. Elle a fait l'étape du cartable. Une étape après l'autre. J'ai fait l'étape dite. Oui. Bravo, Nina. Tu as fait du bon travail. Le cartable bleu est fermé, calme. Le gant rouge a retrouvé sa paire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16016,7 +17197,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina est passée par les balançoires.
+narrateur|Elle a pris le doudou.
+narrateur|Elle a fait l'étape du cartable.
+papa|Une étape après l'autre.
+enfant-f|J'ai fait l'étape dite.
+maman|Oui. Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Le cartable bleu est fermé, calme.
+narrateur|Le gant rouge a retrouvé sa paire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16038,7 +17228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16132,6 +17322,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-035.xlsx
+++ b/stories/arbres/TREE-AUT-035.xlsx
@@ -1591,17 +1591,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. Pose les paumes sur le métal, un moment. Ses doigts deviennent roses, un à un. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.</t>
+          <t>Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. En le ramassant, sa main nue touche le zinc. Le métal est tiède, et ses doigts s'ouvrent dessus. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. Pose les paumes sur le métal, un moment. Ses doigts deviennent roses, un à un. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. En le ramassant, sa main nue touche le zinc. Le métal est tiède, et ses doigts s'ouvrent dessus. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. Pose les paumes sur le métal, un moment. Ses doigts deviennent roses, un à un. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina court vers le bac, le manteau ouvert. Le sable mouillé luit, gris et froid. Une petite pelle jaune attend au bord. La pelle, je la prends ! Sa main nue serre le manche. Le bois pique, et la pelle reste collée. Je n'y arrive pas. Ton autre gant, il est où ? Nina rentre au vestiaire, les épaules basses. Les crochets sont froids sous ses doigts. Le radiateur fait tic, contre le zinc. Elle accroche le manteau, lourd, d'un coup. Le gant rouge attend contre le mur. Toi, je t'avais oublié. En le ramassant, sa main nue touche le zinc. Le métal est tiède, et ses doigts s'ouvrent dessus. La pelle, maintenant. Nina s'agenouille près du bac. Le sable reste frais, mais ses mains tiennent.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1753,8 +1753,8 @@
 narrateur|Elle accroche le manteau, lourd, d'un coup.
 narrateur|Le gant rouge attend contre le mur.
 enfant-f|Toi, je t'avais oublié.
-maman|Pose les paumes sur le métal, un moment.
-narrateur|Ses doigts deviennent roses, un à un.
+narrateur|En le ramassant, sa main nue touche le zinc.
+narrateur|Le métal est tiède, et ses doigts s'ouvrent dessus.
 enfant-f|La pelle, maintenant.
 narrateur|Nina s'agenouille près du bac.
 narrateur|Le sable reste frais, mais ses mains tiennent.</t>
@@ -1789,17 +1789,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les mains où, pour les réchauffer ?</t>
+          <t>Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les mains où, près du tic ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; où, pour les réchauffer ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; où, près du tic ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;soft&gt;&lt;slow&gt;Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les &lt;emphasis&gt;mains&lt;/emphasis&gt; où, pour les réchauffer ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina n'arrivait pas à tenir la pelle, près du bac. Elle a posé les &lt;emphasis&gt;mains&lt;/emphasis&gt; où, près du tic ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Nina n'arrivait pas à tenir la pelle, près du bac.
-maman|Elle a posé les mains où, pour les réchauffer ?</t>
+maman|Elle a posé les mains où, près du tic ?</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui, sur le radiateur. Le gant rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et cette fois elle cède.</t>
+          <t>Oui, sur le radiateur. Le gant rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et le manche cède.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui, sur le radiateur. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et cette fois elle cède.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui, sur le radiateur. Le &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt; rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et le manche cède.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Oui, sur le radiateur. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et cette fois elle cède. [pause]</t>
+          <t>Oui, sur le radiateur. Le &lt;emphasis&gt;gant&lt;/emphasis&gt; rouge a retrouvé ta main. Mes doigts sont roses. Merci d'être revenue le chercher. Un grain de sable brille sur son genou. La pelle jaune attend, et le manche cède. [pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2126,7 +2126,7 @@
 enfant-f|Mes doigts sont roses.
 papa|Merci d'être revenue le chercher.
 narrateur|Un grain de sable brille sur son genou.
-narrateur|La pelle jaune attend, et cette fois elle cède.</t>
+narrateur|La pelle jaune attend, et le manche cède.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -3486,17 +3486,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé s'appuie contre le cartable fermé. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle.</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé attend contre sa jambe, le temps du clic. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé s'appuie contre le cartable fermé. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé attend contre sa jambe, le temps du clic. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé s'appuie contre le cartable fermé. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle. [pause]</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin, tout au fond, sans le froisser. Le ballon sablé attend contre sa jambe, le temps du clic. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le gant rouge a retrouvé sa paire, près de la boucle. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
 narrateur|Nina ouvre la boucle, clic, sans la forcer.
 narrateur|Un dessin à la craie est plié au fond.
 narrateur|Elle pousse le dessin, tout au fond, sans le froisser.
-narrateur|Le ballon sablé s'appuie contre le cartable fermé.
+narrateur|Le ballon sablé attend contre sa jambe, le temps du clic.
 maman|Tu refermes ?
 enfant-f|Oui.
 narrateur|Clic, le cartable redevient un carré fermé.
@@ -3860,17 +3860,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Les deux gants, et plus doucement. Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant.</t>
+          <t>Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Tu veux réessayer des deux mains ? Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Les deux gants, et plus doucement. Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Tu veux réessayer des deux mains ? Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Les deux gants, et plus doucement. Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant. [pause]</t>
+          <t>Le seau bleu a une anse qui brille, près du bac. Le seau ! Nina attrape l'anse trop vite. Ting, le seau bascule, vide. Il m'a échappé. Tu veux réessayer des deux mains ? Elle reprend l'anse, et le métal ne pique plus. Tu remplis un peu ? Oui, un peu de sable. Le sable coule, chh, dans le bleu. Nina pose le seau au bord du bac. Il est à toi, maintenant. [pause]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
 narrateur|Nina attrape l'anse trop vite.
 narrateur|Ting, le seau bascule, vide.
 enfant-f|Il m'a échappé.
-papa|Les deux gants, et plus doucement.
+papa|Tu veux réessayer des deux mains ?
 narrateur|Elle reprend l'anse, et le métal ne pique plus.
 maman|Tu remplis un peu ?
 enfant-f|Oui, un peu de sable.
@@ -4991,17 +4991,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina glisse le dessin derrière le seau, le temps d'ouvrir.</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le seau veille, et la paire rouge se touche.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina glisse le dessin derrière le seau, le temps d'ouvrir.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le seau veille, et la paire rouge se touche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina glisse le dessin derrière le seau, le temps d'ouvrir. [pause]</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Elle pousse le dessin au fond, puis reprend l'anse. Le seau bleu se pose à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le seau veille, et la paire rouge se touche. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5146,7 +5146,7 @@
 maman|Tu refermes ?
 enfant-f|Oui.
 narrateur|Clic, le cartable redevient un carré fermé.
-narrateur|Nina glisse le dessin derrière le seau, le temps d'ouvrir.</t>
+narrateur|Le seau veille, et la paire rouge se touche.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. Secoue l'oreille, puis pose-le au sec. Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main.</t>
+          <t>Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. L'oreille, tu la mets où, au sec ? Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. Secoue l'oreille, puis pose-le au sec. Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. L'oreille, tu la mets où, au sec ? Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. Secoue l'oreille, puis pose-le au sec. Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main. [pause]</t>
+          <t>Le doudou beige attend sur le banc, près du bac. Une oreille est pliée, un peu humide. Le doudou ! Nina le serre contre sa joue. Le tissu froid la fait grimacer. Il a froid, lui aussi. L'oreille, tu la mets où, au sec ? Elle secoue, et un grain de sable tombe. Elle l'assoit sur le bord de bois du bac. Il t'attend, pendant que tu creuses ? Oui, il regarde la pelle. Le tissu reprend une chaleur de main. [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5515,7 +5515,7 @@
 narrateur|Nina le serre contre sa joue.
 narrateur|Le tissu froid la fait grimacer.
 enfant-f|Il a froid, lui aussi.
-maman|Secoue l'oreille, puis pose-le au sec.
+maman|L'oreille, tu la mets où, au sec ?
 narrateur|Elle secoue, et un grain de sable tombe.
 narrateur|Elle l'assoit sur le bord de bois du bac.
 papa|Il t'attend, pendant que tu creuses ?
@@ -6496,17 +6496,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Le tissu touche la laine du manteau, au crochet. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina souffle le grain, puis pousse le dessin au fond.</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina souffle le grain, puis pousse le dessin au fond. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le tissu touche la laine du manteau, au crochet.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Le tissu touche la laine du manteau, au crochet. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina souffle le grain, puis pousse le dessin au fond.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina souffle le grain, puis pousse le dessin au fond. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le tissu touche la laine du manteau, au crochet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Le tissu touche la laine du manteau, au crochet. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina souffle le grain, puis pousse le dessin au fond. [pause]</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina souffle le grain, puis pousse le dessin au fond. Le doudou glisse contre le cartable, l'oreille sablée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Le tissu touche la laine du manteau, au crochet. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6646,12 +6646,12 @@
 enfant-f|J'ouvre.
 narrateur|Nina ouvre la boucle, clic, sans la forcer.
 narrateur|Un dessin à la craie est plié au fond.
-narrateur|Le tissu touche la laine du manteau, au crochet.
+narrateur|Nina souffle le grain, puis pousse le dessin au fond.
 narrateur|Le doudou glisse contre le cartable, l'oreille sablée.
 maman|Tu refermes ?
 enfant-f|Oui.
 narrateur|Clic, le cartable redevient un carré fermé.
-narrateur|Nina souffle le grain, puis pousse le dessin au fond.</t>
+narrateur|Le tissu touche la laine du manteau, au crochet.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tes paumes, sur le tiède. Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Cette fois, les deux gants tiennent la rampe.</t>
+          <t>Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tu as trouvé le tiède ? Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Les deux gants tiennent la rampe, sans lâcher.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tes paumes, sur le tiède. Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Cette fois, les deux gants tiennent la rampe.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tu as trouvé le tiède ? Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Les deux gants tiennent la rampe, sans lâcher.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tes paumes, sur le tiède. Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Cette fois, les deux gants tiennent la rampe.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina pose un pied sur la marche du toboggan. Le plastique jaune est mouillé, glissant. Le manteau ouvert claque contre ses genoux. Je monte ! Sa main nue cherche la rampe. Le métal pince, et elle lâche tout. C'est trop froid. Le gant rouge est resté derrière. Nina revient vers le vestiaire, sans parler. Le radiateur ronronne, bas, contre le mur. Elle accroche le manteau, et les boutons tapent. L'autre gant rouge attend au pied du zinc. Tu as trouvé le tiède ? Elle pose les deux mains, et le tic marque le temps. Mes doigts reviennent. La rampe t'attendra. Nina reprend la première marche. Une goutte pend sous le rebord, ronde. Les deux gants tiennent la rampe, sans lâcher.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -7030,13 +7030,13 @@
 narrateur|Le radiateur ronronne, bas, contre le mur.
 narrateur|Elle accroche le manteau, et les boutons tapent.
 narrateur|L'autre gant rouge attend au pied du zinc.
-maman|Tes paumes, sur le tiède.
+maman|Tu as trouvé le tiède ?
 narrateur|Elle pose les deux mains, et le tic marque le temps.
 enfant-f|Mes doigts reviennent.
 papa|La rampe t'attendra.
 narrateur|Nina reprend la première marche.
 narrateur|Une goutte pend sous le rebord, ronde.
-narrateur|Cette fois, les deux gants tiennent la rampe.</t>
+narrateur|Les deux gants tiennent la rampe, sans lâcher.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -7068,17 +7068,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Nina a lâché la rampe du toboggan, trop froide. Elle a posé les mains où, ensuite ?</t>
+          <t>Nina a lâché la rampe du toboggan, trop froide. Elle a posé les mains où, au vestiaire ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina a lâché la rampe du toboggan, trop froide. Elle a posé les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; où, ensuite ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nina a lâché la rampe du toboggan, trop froide. Elle a posé les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; où, au vestiaire ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>&lt;soft&gt;&lt;slow&gt;Nina a lâché la rampe du toboggan, trop froide. Elle a posé les &lt;emphasis&gt;mains&lt;/emphasis&gt; où, ensuite ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nina a lâché la rampe du toboggan, trop froide. Elle a posé les &lt;emphasis&gt;mains&lt;/emphasis&gt; où, au vestiaire ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       <c r="AW33" t="inlineStr">
         <is>
           <t>narrateur|Nina a lâché la rampe du toboggan, trop froide.
-papa|Elle a posé les mains où, ensuite ?</t>
+papa|Elle a posé les mains où, au vestiaire ?</t>
         </is>
       </c>
     </row>
@@ -9139,17 +9139,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Pose-le où tes pieds ne le pousseront pas. Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire.</t>
+          <t>Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Où tes pieds ne le pousseront pas ? Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Pose-le où tes pieds ne le pousseront pas. Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Où tes pieds ne le pousseront pas ? Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Pose-le où tes pieds ne le pousseront pas. Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire. [pause]</t>
+          <t>Le seau bleu attend au pied des marches jaunes. Le seau, maman. Nina soulève l'anse d'un coup. Ting, une goutte du rebord tombe dedans. Il a pris l'eau tout seul. Où tes pieds ne le pousseront pas ? Elle le cale contre la première marche. Il est à sa place ? Oui, papa. L'anse ne pique plus sous le gant. Un oiseau crie une fois, très haut. On entend même le seau se taire. [pause]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
 narrateur|Nina soulève l'anse d'un coup.
 narrateur|Ting, une goutte du rebord tombe dedans.
 enfant-f|Il a pris l'eau tout seul.
-papa|Pose-le où tes pieds ne le pousseront pas.
+papa|Où tes pieds ne le pousseront pas ?
 narrateur|Elle le cale contre la première marche.
 maman|Il est à sa place ?
 enfant-f|Oui, papa.
@@ -10270,17 +10270,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. L'anse attend, et le cartable redevient carré. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, à côté d'un crayon.</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, à côté d'un crayon. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. L'anse reste contre le cuir, sans coincer.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. L'anse attend, et le cartable redevient carré. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, à côté d'un crayon.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, à côté d'un crayon. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. L'anse reste contre le cuir, sans coincer.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. L'anse attend, et le cartable redevient carré. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, à côté d'un crayon. [pause]</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, à côté d'un crayon. Le seau tapote la boucle, ting, puis se tait. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. L'anse reste contre le cuir, sans coincer. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10420,12 +10420,12 @@
 enfant-f|J'ouvre.
 narrateur|Nina ouvre la boucle, clic, sans la forcer.
 narrateur|Un dessin à la craie est plié au fond.
-narrateur|L'anse attend, et le cartable redevient carré.
+narrateur|Nina pousse le dessin au fond, à côté d'un crayon.
 narrateur|Le seau tapote la boucle, ting, puis se tait.
 maman|Tu refermes ?
 enfant-f|Oui.
 narrateur|Clic, le cartable redevient un carré fermé.
-narrateur|Nina pousse le dessin au fond, à côté d'un crayon.</t>
+narrateur|L'anse reste contre le cuir, sans coincer.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -12149,17 +12149,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Les paumes sur le métal, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.</t>
+          <t>Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Le zinc est tiède, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Les paumes sur le métal, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Le zinc est tiède, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Les paumes sur le métal, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Nina s'assoit sur le siège des balançoires. Le bois est frais, et les chaînes font cling. Une main gantée tient, l'autre reste nue. J'y vais ! La chaîne nue pince sa paume. Elle ne peut pas pousser des deux côtés. Il me manque un gant. Il est près du radiateur, je crois. Nina quitte le siège, les épaules basses. Au vestiaire, le radiateur fait tic, tic. Elle accroche le manteau sur le crochet bas. La paire de gants se retrouve, rouge contre rouge. Le zinc est tiède, tu sens ? Oui, les doigts se colorent, roses. Ils sont chauds. Les chaînes, si tu veux. Nina reprend le siège. Les deux mains tiennent, et les chaînes acceptent. La cour sent l'herbe mouillée, tout autour.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -12309,7 +12309,7 @@
 narrateur|Au vestiaire, le radiateur fait tic, tic.
 narrateur|Elle accroche le manteau sur le crochet bas.
 narrateur|La paire de gants se retrouve, rouge contre rouge.
-papa|Les paumes sur le métal, tu sens ?
+papa|Le zinc est tiède, tu sens ?
 narrateur|Oui, les doigts se colorent, roses.
 enfant-f|Ils sont chauds.
 maman|Les chaînes, si tu veux.
@@ -12535,17 +12535,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui, les mains sur le radiateur. La paire de gants est complète. Je peux tenir les deux chaînes. Merci d'avoir écouté le tic. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent.</t>
+          <t>Oui, les mains sur le radiateur. La paire de gants est complète. Je peux tenir les deux chaînes. Merci, tes deux mains tiennent. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui, les mains sur le radiateur. La paire de &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;s est complète. Je peux tenir les deux chaînes. Merci d'avoir écouté le tic. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui, les mains sur le radiateur. La paire de &lt;emphasis level="moderate"&gt;gant&lt;/emphasis&gt;s est complète. Je peux tenir les deux chaînes. Merci, tes deux mains tiennent. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Oui, les mains sur le radiateur. La paire de &lt;emphasis&gt;gant&lt;/emphasis&gt;s est complète. Je peux tenir les deux chaînes. Merci d'avoir écouté le tic. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent. [pause]</t>
+          <t>Oui, les mains sur le radiateur. La paire de &lt;emphasis&gt;gant&lt;/emphasis&gt;s est complète. Je peux tenir les deux chaînes. Merci, tes deux mains tiennent. Une ombre d'oiseau passe sur le bois. Le siège reste frais, mais les paumes tiennent. [pause]</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -12682,7 +12682,7 @@
           <t>papa|Oui, les mains sur le radiateur.
 maman|La paire de gants est complète.
 enfant-f|Je peux tenir les deux chaînes.
-papa|Merci d'avoir écouté le tic.
+papa|Merci, tes deux mains tiennent.
 narrateur|Une ombre d'oiseau passe sur le bois.
 narrateur|Le siège reste frais, mais les paumes tiennent.</t>
         </is>
@@ -13485,17 +13485,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, d'abord. Nina croque la pomme, les deux gants fermés sur le fruit. Le fil d'argent coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.</t>
+          <t>Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, au premier essai. Nina croque la pomme, les deux gants fermés sur le fruit. Le fil d'argent coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, d'abord. Nina croque la pomme, les deux gants fermés sur le fruit. Le &lt;emphasis level="moderate"&gt;fil d'argent&lt;/emphasis&gt; coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, au premier essai. Nina croque la pomme, les deux gants fermés sur le fruit. Le &lt;emphasis level="moderate"&gt;fil d'argent&lt;/emphasis&gt; coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, d'abord. Nina croque la pomme, les deux gants fermés sur le fruit. Le &lt;emphasis&gt;fil d'argent&lt;/emphasis&gt; coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le ballon dort entre les pieds du pilier, loin des chaînes. Il ne s'envole plus. Tu l'as mis trop haut, au premier essai. Nina croque la pomme, les deux gants fermés sur le fruit. Le &lt;emphasis&gt;fil d'argent&lt;/emphasis&gt; coupe le ciel de la vitre, très net. Les chaînes se taisent, de l'autre côté. Moi, je tiens les deux, maintenant. Le radiateur tic, et le bois du préau sent le sec.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13635,7 +13635,7 @@
         <is>
           <t>narrateur|Le ballon dort entre les pieds du pilier, loin des chaînes.
 enfant-f|Il ne s'envole plus.
-maman|Tu l'as mis trop haut, d'abord.
+maman|Tu l'as mis trop haut, au premier essai.
 narrateur|Nina croque la pomme, les deux gants fermés sur le fruit.
 narrateur|Le fil d'argent coupe le ciel de la vitre, très net.
 papa|Les chaînes se taisent, de l'autre côté.
@@ -15550,17 +15550,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Ting, le cartable et le seau se taisent ensemble. Le seau bleu reste à côté de la boucle fermée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, puis tapote l'anse.</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, puis tapote l'anse. Le seau bleu reste à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Ting, le cartable et le seau se taisent ensemble.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Ting, le cartable et le seau se taisent ensemble. Le seau bleu reste à côté de la boucle fermée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, puis tapote l'anse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, puis tapote l'anse. Le seau bleu reste à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Ting, le cartable et le seau se taisent ensemble.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Ting, le cartable et le seau se taisent ensemble. Le seau bleu reste à côté de la boucle fermée. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Nina pousse le dessin au fond, puis tapote l'anse. [pause]</t>
+          <t>Le cartable bleu attend près du vestiaire, un peu lourd. La boucle est froide sous le pouce. On ouvre ? J'ouvre. Nina ouvre la boucle, clic, sans la forcer. Un dessin à la craie est plié au fond. Nina pousse le dessin au fond, puis tapote l'anse. Le seau bleu reste à côté de la boucle. Tu refermes ? Oui. Clic, le cartable redevient un carré fermé. Ting, le cartable et le seau se taisent ensemble. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15700,12 +15700,12 @@
 enfant-f|J'ouvre.
 narrateur|Nina ouvre la boucle, clic, sans la forcer.
 narrateur|Un dessin à la craie est plié au fond.
-narrateur|Ting, le cartable et le seau se taisent ensemble.
-narrateur|Le seau bleu reste à côté de la boucle fermée.
+narrateur|Nina pousse le dessin au fond, puis tapote l'anse.
+narrateur|Le seau bleu reste à côté de la boucle.
 maman|Tu refermes ?
 enfant-f|Oui.
 narrateur|Clic, le cartable redevient un carré fermé.
-narrateur|Nina pousse le dessin au fond, puis tapote l'anse.</t>
+narrateur|Ting, le cartable et le seau se taisent ensemble.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -17423,7 +17423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17536,6 +17536,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
